--- a/class_diagram/controller/students/クラス図 controller.students_成績管理システム.xlsx
+++ b/class_diagram/controller/students/クラス図 controller.students_成績管理システム.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ktc\Downloads\controller\students\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri34ys\seiseki_manage_sys\class_diagram\controller\students\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF35624A-CEB3-4137-810C-004C3AFFE90A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11115D1C-3D9F-4111-AD0D-276BE6D71439}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="31665" windowHeight="16005" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="31665" windowHeight="16005" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller.LoginServlet" sheetId="26" r:id="rId1"/>
     <sheet name="controller.ScoreGetServlet" sheetId="38" r:id="rId2"/>
+    <sheet name="controller.ClassesGetServlet" sheetId="40" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -658,6 +659,552 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{034EABA0-D50B-42A2-BB62-EE5A383B043B}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{62D721A1-14B6-419C-825A-BB043EBCFB7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1362075" y="1743075"/>
+          <a:ext cx="5486400" cy="4953000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0"/>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t># doGet(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t># doPost(request : HttpServletRequest ,response :  HttpServletResponse) : void</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5DAC3A4-9436-4394-8E79-346A56FD64B3}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{15723AC8-7A10-4908-982D-E38FEF435220}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="952500"/>
+          <a:ext cx="5495925" cy="1000125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" marR="0" indent="0" algn="l">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600"/>
+            <a:t>ClassesGetServlet</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69B38BB6-C598-41B8-B07D-7A75DF35B901}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
               <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{62D721A1-14B6-419C-825A-BB043EBCFB7A}"/>
@@ -1369,4 +1916,16 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53439311-C692-4ACF-B0B0-FEC0332E944B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="7"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>